--- a/Shablon/34401A_gost.xlsx
+++ b/Shablon/34401A_gost.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="214">
   <si>
     <t>Предел измерений</t>
   </si>
@@ -86,15 +86,6 @@
   </si>
   <si>
     <t>5 кГц</t>
-  </si>
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
   </si>
   <si>
     <t xml:space="preserve">Наименование и тип СИ: </t>
@@ -740,12 +731,6 @@
       </rPr>
       <t xml:space="preserve"> 5)°С</t>
     </r>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре акредитованных лиц № РОСС СОБ 3.00231.2014</t>
   </si>
   <si>
     <t>Заключение:</t>
@@ -1109,100 +1094,100 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1517,87 +1502,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="62"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="73" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="72"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="69" t="str">
+      <c r="A7" s="64" t="str">
         <f>"Протокол поверки № 10/"&amp;C199&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
@@ -1610,29 +1585,29 @@
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="3" t="s">
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="53" t="s">
         <v>25</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="74" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="75" t="s">
-        <v>28</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1640,11 +1615,11 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="68" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
+      <c r="A11" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1652,13 +1627,13 @@
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
+      <c r="A12" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
       <c r="D12" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1666,13 +1641,13 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="68" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="75" t="s">
-        <v>33</v>
+      <c r="A13" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="53" t="s">
+        <v>30</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1680,13 +1655,13 @@
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="68" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
+      <c r="A14" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
       <c r="D14" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -1694,13 +1669,13 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="68" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
+      <c r="A15" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -1719,113 +1694,113 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="42"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="58" t="s">
+      <c r="G19" s="60"/>
+      <c r="H19" s="42"/>
+    </row>
+    <row r="20" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58" t="s">
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="42"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58" t="s">
+      <c r="E20" s="59"/>
+      <c r="F20" s="60" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" s="60"/>
+      <c r="H20" s="42"/>
+    </row>
+    <row r="21" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="58"/>
-      <c r="H19" s="42"/>
-    </row>
-    <row r="20" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="71" t="s">
+      <c r="E21" s="59"/>
+      <c r="F21" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="71"/>
-      <c r="F20" s="58" t="s">
-        <v>214</v>
-      </c>
-      <c r="G20" s="58"/>
-      <c r="H20" s="42"/>
-    </row>
-    <row r="21" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="70" t="s">
+      <c r="G21" s="60"/>
+      <c r="H21" s="42"/>
+    </row>
+    <row r="22" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="71" t="s">
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="71"/>
-      <c r="F21" s="58" t="s">
+      <c r="E22" s="59"/>
+      <c r="F22" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="G21" s="58"/>
-      <c r="H21" s="42"/>
-    </row>
-    <row r="22" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="70" t="s">
+      <c r="G22" s="60"/>
+      <c r="H22" s="42"/>
+    </row>
+    <row r="23" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="71" t="s">
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="71"/>
-      <c r="F22" s="58" t="s">
+      <c r="G23" s="60"/>
+      <c r="H23" s="42"/>
+    </row>
+    <row r="24" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="58"/>
-      <c r="H22" s="42"/>
-    </row>
-    <row r="23" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="58" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23" s="58"/>
-      <c r="H23" s="42"/>
-    </row>
-    <row r="24" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" s="58"/>
+      <c r="G24" s="60"/>
       <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
@@ -1840,7 +1815,7 @@
     </row>
     <row r="26" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -1861,17 +1836,17 @@
     </row>
     <row r="28" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -1883,7 +1858,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -1894,30 +1869,30 @@
       <c r="H31" s="15"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="57" t="s">
+      <c r="A32" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57" t="s">
+      <c r="B32" s="69"/>
+      <c r="C32" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57" t="s">
+      <c r="F32" s="69"/>
+      <c r="G32" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="57"/>
+      <c r="H32" s="69"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="57"/>
-      <c r="B33" s="57"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
+      <c r="A33" s="69"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
       <c r="G33" s="48" t="s">
         <v>18</v>
       </c>
@@ -1926,10 +1901,10 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="57">
+      <c r="A34" s="69">
         <v>100</v>
       </c>
-      <c r="B34" s="59" t="s">
+      <c r="B34" s="68" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="17">
@@ -1938,10 +1913,10 @@
       <c r="D34" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E34" s="76" t="s">
-        <v>69</v>
-      </c>
-      <c r="F34" s="76"/>
+      <c r="E34" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" s="73"/>
       <c r="G34" s="49">
         <v>9.9960000000000004</v>
       </c>
@@ -1950,18 +1925,18 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="57"/>
-      <c r="B35" s="59"/>
+      <c r="A35" s="69"/>
+      <c r="B35" s="68"/>
       <c r="C35" s="17">
         <v>50</v>
       </c>
       <c r="D35" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E35" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="76"/>
+      <c r="E35" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="F35" s="73"/>
       <c r="G35" s="49">
         <v>49.994</v>
       </c>
@@ -1970,18 +1945,18 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="57"/>
-      <c r="B36" s="59"/>
+      <c r="A36" s="69"/>
+      <c r="B36" s="68"/>
       <c r="C36" s="17">
         <v>100</v>
       </c>
       <c r="D36" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E36" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="F36" s="76"/>
+      <c r="E36" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36" s="73"/>
       <c r="G36" s="49">
         <v>99.991500000000002</v>
       </c>
@@ -1990,18 +1965,18 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="57"/>
-      <c r="B37" s="59"/>
+      <c r="A37" s="69"/>
+      <c r="B37" s="68"/>
       <c r="C37" s="17">
         <v>-100</v>
       </c>
       <c r="D37" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="76" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" s="76"/>
+      <c r="E37" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="73"/>
       <c r="G37" s="49">
         <v>-100.0085</v>
       </c>
@@ -2010,10 +1985,10 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="57">
+      <c r="A38" s="69">
         <v>1</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="68" t="s">
         <v>3</v>
       </c>
       <c r="C38" s="17">
@@ -2022,10 +1997,10 @@
       <c r="D38" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E38" s="76" t="s">
-        <v>73</v>
-      </c>
-      <c r="F38" s="76"/>
+      <c r="E38" s="73" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="73"/>
       <c r="G38" s="49">
         <v>9.9988999999999995E-2</v>
       </c>
@@ -2034,18 +2009,18 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="57"/>
-      <c r="B39" s="59"/>
+      <c r="A39" s="69"/>
+      <c r="B39" s="68"/>
       <c r="C39" s="17">
         <v>0.5</v>
       </c>
       <c r="D39" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="76" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" s="76"/>
+      <c r="E39" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="73"/>
       <c r="G39" s="49">
         <v>0.499973</v>
       </c>
@@ -2054,18 +2029,18 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="57"/>
-      <c r="B40" s="59"/>
+      <c r="A40" s="69"/>
+      <c r="B40" s="68"/>
       <c r="C40" s="17">
         <v>1</v>
       </c>
       <c r="D40" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E40" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="76"/>
+      <c r="E40" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="F40" s="73"/>
       <c r="G40" s="49">
         <v>0.99995299999999998</v>
       </c>
@@ -2074,18 +2049,18 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="57"/>
-      <c r="B41" s="59"/>
+      <c r="A41" s="69"/>
+      <c r="B41" s="68"/>
       <c r="C41" s="17">
         <v>-1</v>
       </c>
       <c r="D41" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E41" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="F41" s="76"/>
+      <c r="E41" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="73"/>
       <c r="G41" s="49">
         <v>-1.0000469999999999</v>
       </c>
@@ -2094,10 +2069,10 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="59">
+      <c r="A42" s="68">
         <v>10</v>
       </c>
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="68" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="17">
@@ -2106,10 +2081,10 @@
       <c r="D42" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="76" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="76"/>
+      <c r="E42" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="73"/>
       <c r="G42" s="49">
         <v>0.999915</v>
       </c>
@@ -2118,18 +2093,18 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="59"/>
-      <c r="B43" s="59"/>
+      <c r="A43" s="68"/>
+      <c r="B43" s="68"/>
       <c r="C43" s="17">
         <v>5</v>
       </c>
       <c r="D43" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="76" t="s">
-        <v>78</v>
-      </c>
-      <c r="F43" s="76"/>
+      <c r="E43" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="73"/>
       <c r="G43" s="49">
         <v>4.9997749999999996</v>
       </c>
@@ -2138,18 +2113,18 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="59"/>
-      <c r="B44" s="59"/>
+      <c r="A44" s="68"/>
+      <c r="B44" s="68"/>
       <c r="C44" s="17">
         <v>10</v>
       </c>
       <c r="D44" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="76" t="s">
-        <v>79</v>
-      </c>
-      <c r="F44" s="76"/>
+      <c r="E44" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="73"/>
       <c r="G44" s="49">
         <v>9.9995999999999992</v>
       </c>
@@ -2158,18 +2133,18 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="59"/>
-      <c r="B45" s="59"/>
+      <c r="A45" s="68"/>
+      <c r="B45" s="68"/>
       <c r="C45" s="17">
         <v>-10</v>
       </c>
       <c r="D45" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="F45" s="76"/>
+      <c r="E45" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" s="73"/>
       <c r="G45" s="49">
         <v>-10.000400000000001</v>
       </c>
@@ -2178,10 +2153,10 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="59">
+      <c r="A46" s="68">
         <v>100</v>
       </c>
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="68" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="17">
@@ -2190,10 +2165,10 @@
       <c r="D46" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E46" s="76" t="s">
-        <v>81</v>
-      </c>
-      <c r="F46" s="76"/>
+      <c r="E46" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="73"/>
       <c r="G46" s="49">
         <v>9.9995499999999993</v>
       </c>
@@ -2202,18 +2177,18 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="59"/>
-      <c r="B47" s="59"/>
+      <c r="A47" s="68"/>
+      <c r="B47" s="68"/>
       <c r="C47" s="17">
         <v>50</v>
       </c>
       <c r="D47" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="F47" s="76"/>
+      <c r="E47" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="F47" s="73"/>
       <c r="G47" s="49">
         <v>49.997149999999998</v>
       </c>
@@ -2222,18 +2197,18 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="59"/>
-      <c r="B48" s="59"/>
+      <c r="A48" s="68"/>
+      <c r="B48" s="68"/>
       <c r="C48" s="17">
         <v>100</v>
       </c>
       <c r="D48" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="F48" s="76"/>
+      <c r="E48" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="73"/>
       <c r="G48" s="49">
         <v>99.994900000000001</v>
       </c>
@@ -2242,18 +2217,18 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="59"/>
-      <c r="B49" s="59"/>
+      <c r="A49" s="68"/>
+      <c r="B49" s="68"/>
       <c r="C49" s="17">
         <v>-100</v>
       </c>
       <c r="D49" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E49" s="76" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" s="76"/>
+      <c r="E49" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" s="73"/>
       <c r="G49" s="49">
         <v>-100.0051</v>
       </c>
@@ -2262,10 +2237,10 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="57">
+      <c r="A50" s="69">
         <v>1000</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="68" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="17">
@@ -2274,10 +2249,10 @@
       <c r="D50" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E50" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="F50" s="76"/>
+      <c r="E50" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="F50" s="73"/>
       <c r="G50" s="49">
         <v>99.985500000000002</v>
       </c>
@@ -2286,18 +2261,18 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="57"/>
-      <c r="B51" s="59"/>
+      <c r="A51" s="69"/>
+      <c r="B51" s="68"/>
       <c r="C51" s="17">
         <v>500</v>
       </c>
       <c r="D51" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E51" s="76" t="s">
-        <v>86</v>
-      </c>
-      <c r="F51" s="76"/>
+      <c r="E51" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="F51" s="73"/>
       <c r="G51" s="49">
         <v>499.96749999999997</v>
       </c>
@@ -2306,18 +2281,18 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="57"/>
-      <c r="B52" s="59"/>
+      <c r="A52" s="69"/>
+      <c r="B52" s="68"/>
       <c r="C52" s="17">
         <v>1000</v>
       </c>
       <c r="D52" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="76" t="s">
-        <v>87</v>
-      </c>
-      <c r="F52" s="76"/>
+      <c r="E52" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="F52" s="73"/>
       <c r="G52" s="49">
         <v>999.94500000000005</v>
       </c>
@@ -2326,18 +2301,18 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="57"/>
-      <c r="B53" s="59"/>
+      <c r="A53" s="69"/>
+      <c r="B53" s="68"/>
       <c r="C53" s="17">
         <v>-1000</v>
       </c>
       <c r="D53" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E53" s="76" t="s">
-        <v>88</v>
-      </c>
-      <c r="F53" s="76"/>
+      <c r="E53" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53" s="73"/>
       <c r="G53" s="49">
         <v>-1000.0549999999999</v>
       </c>
@@ -2347,38 +2322,38 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G54" s="18"/>
       <c r="H54" s="18"/>
     </row>
     <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="57" t="s">
+      <c r="A55" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B55" s="57"/>
-      <c r="C55" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57" t="s">
+      <c r="B55" s="69"/>
+      <c r="C55" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="69"/>
+      <c r="E55" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="F55" s="57" t="s">
+      <c r="F55" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="G55" s="65" t="s">
+      <c r="G55" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="H55" s="65"/>
+      <c r="H55" s="74"/>
     </row>
     <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="57"/>
-      <c r="B56" s="57"/>
-      <c r="C56" s="57"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="57"/>
-      <c r="F56" s="57"/>
+      <c r="A56" s="69"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="69"/>
+      <c r="F56" s="69"/>
       <c r="G56" s="50" t="s">
         <v>18</v>
       </c>
@@ -2387,23 +2362,23 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="57">
+      <c r="A57" s="69">
         <v>100</v>
       </c>
-      <c r="B57" s="57" t="s">
+      <c r="B57" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="62">
+      <c r="C57" s="75">
         <v>10</v>
       </c>
-      <c r="D57" s="59" t="s">
+      <c r="D57" s="68" t="s">
         <v>2</v>
       </c>
       <c r="E57" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F57" s="77" t="s">
-        <v>89</v>
+      <c r="F57" s="54" t="s">
+        <v>86</v>
       </c>
       <c r="G57" s="49">
         <v>9.9250000000000007</v>
@@ -2413,15 +2388,15 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="57"/>
-      <c r="B58" s="57"/>
-      <c r="C58" s="62"/>
-      <c r="D58" s="59"/>
+      <c r="A58" s="69"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="68"/>
       <c r="E58" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="77" t="s">
-        <v>90</v>
+      <c r="F58" s="54" t="s">
+        <v>87</v>
       </c>
       <c r="G58" s="49">
         <v>9.9540000000000006</v>
@@ -2431,15 +2406,15 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A59" s="57"/>
-      <c r="B59" s="57"/>
-      <c r="C59" s="62"/>
-      <c r="D59" s="59"/>
+      <c r="A59" s="69"/>
+      <c r="B59" s="69"/>
+      <c r="C59" s="75"/>
+      <c r="D59" s="68"/>
       <c r="E59" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F59" s="77" t="s">
-        <v>91</v>
+      <c r="F59" s="54" t="s">
+        <v>88</v>
       </c>
       <c r="G59" s="49">
         <v>9.9380000000000006</v>
@@ -2449,15 +2424,15 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A60" s="57"/>
-      <c r="B60" s="57"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="59"/>
+      <c r="A60" s="69"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="75"/>
+      <c r="D60" s="68"/>
       <c r="E60" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F60" s="77" t="s">
-        <v>92</v>
+      <c r="F60" s="54" t="s">
+        <v>89</v>
       </c>
       <c r="G60" s="49">
         <v>9.86</v>
@@ -2467,19 +2442,19 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="57"/>
-      <c r="B61" s="57"/>
-      <c r="C61" s="62">
+      <c r="A61" s="69"/>
+      <c r="B61" s="69"/>
+      <c r="C61" s="75">
         <v>50</v>
       </c>
-      <c r="D61" s="59" t="s">
+      <c r="D61" s="68" t="s">
         <v>2</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F61" s="77" t="s">
-        <v>93</v>
+      <c r="F61" s="54" t="s">
+        <v>90</v>
       </c>
       <c r="G61" s="49">
         <v>49.784999999999997</v>
@@ -2489,15 +2464,15 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A62" s="57"/>
-      <c r="B62" s="57"/>
-      <c r="C62" s="62"/>
-      <c r="D62" s="59"/>
+      <c r="A62" s="69"/>
+      <c r="B62" s="69"/>
+      <c r="C62" s="75"/>
+      <c r="D62" s="68"/>
       <c r="E62" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F62" s="77" t="s">
-        <v>94</v>
+      <c r="F62" s="54" t="s">
+        <v>91</v>
       </c>
       <c r="G62" s="49">
         <v>49.93</v>
@@ -2507,15 +2482,15 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A63" s="57"/>
-      <c r="B63" s="57"/>
-      <c r="C63" s="62"/>
-      <c r="D63" s="59"/>
+      <c r="A63" s="69"/>
+      <c r="B63" s="69"/>
+      <c r="C63" s="75"/>
+      <c r="D63" s="68"/>
       <c r="E63" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F63" s="77" t="s">
-        <v>95</v>
+      <c r="F63" s="54" t="s">
+        <v>92</v>
       </c>
       <c r="G63" s="49">
         <v>49.89</v>
@@ -2525,15 +2500,15 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A64" s="57"/>
-      <c r="B64" s="57"/>
-      <c r="C64" s="62"/>
-      <c r="D64" s="59"/>
+      <c r="A64" s="69"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="75"/>
+      <c r="D64" s="68"/>
       <c r="E64" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F64" s="77" t="s">
-        <v>96</v>
+      <c r="F64" s="54" t="s">
+        <v>93</v>
       </c>
       <c r="G64" s="49">
         <v>49.62</v>
@@ -2543,15 +2518,15 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A65" s="57"/>
-      <c r="B65" s="57"/>
-      <c r="C65" s="62"/>
-      <c r="D65" s="59"/>
+      <c r="A65" s="69"/>
+      <c r="B65" s="69"/>
+      <c r="C65" s="75"/>
+      <c r="D65" s="68"/>
       <c r="E65" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F65" s="77" t="s">
-        <v>97</v>
+      <c r="F65" s="54" t="s">
+        <v>94</v>
       </c>
       <c r="G65" s="29">
         <v>47.5</v>
@@ -2561,19 +2536,19 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="57"/>
-      <c r="B66" s="57"/>
-      <c r="C66" s="63">
+      <c r="A66" s="69"/>
+      <c r="B66" s="69"/>
+      <c r="C66" s="70">
         <v>100</v>
       </c>
-      <c r="D66" s="59" t="s">
+      <c r="D66" s="68" t="s">
         <v>2</v>
       </c>
       <c r="E66" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F66" s="77" t="s">
-        <v>98</v>
+      <c r="F66" s="54" t="s">
+        <v>95</v>
       </c>
       <c r="G66" s="30">
         <v>99.61</v>
@@ -2583,15 +2558,15 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A67" s="57"/>
-      <c r="B67" s="57"/>
-      <c r="C67" s="63"/>
-      <c r="D67" s="59"/>
+      <c r="A67" s="69"/>
+      <c r="B67" s="69"/>
+      <c r="C67" s="70"/>
+      <c r="D67" s="68"/>
       <c r="E67" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F67" s="77" t="s">
-        <v>99</v>
+      <c r="F67" s="54" t="s">
+        <v>96</v>
       </c>
       <c r="G67" s="30">
         <v>99.9</v>
@@ -2601,15 +2576,15 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A68" s="57"/>
-      <c r="B68" s="57"/>
-      <c r="C68" s="63"/>
-      <c r="D68" s="59"/>
+      <c r="A68" s="69"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="68"/>
       <c r="E68" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F68" s="77" t="s">
-        <v>100</v>
+      <c r="F68" s="54" t="s">
+        <v>97</v>
       </c>
       <c r="G68" s="30">
         <v>99.83</v>
@@ -2619,15 +2594,15 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A69" s="57"/>
-      <c r="B69" s="57"/>
-      <c r="C69" s="63"/>
-      <c r="D69" s="59"/>
+      <c r="A69" s="69"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="68"/>
       <c r="E69" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="77" t="s">
-        <v>101</v>
+      <c r="F69" s="54" t="s">
+        <v>98</v>
       </c>
       <c r="G69" s="30">
         <v>99.32</v>
@@ -2637,15 +2612,15 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A70" s="57"/>
-      <c r="B70" s="57"/>
-      <c r="C70" s="63"/>
-      <c r="D70" s="59"/>
+      <c r="A70" s="69"/>
+      <c r="B70" s="69"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="68"/>
       <c r="E70" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F70" s="77" t="s">
-        <v>102</v>
+      <c r="F70" s="54" t="s">
+        <v>99</v>
       </c>
       <c r="G70" s="30">
         <v>95.5</v>
@@ -2655,10 +2630,10 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A71" s="64">
+      <c r="A71" s="65">
         <v>1</v>
       </c>
-      <c r="B71" s="64" t="s">
+      <c r="B71" s="65" t="s">
         <v>3</v>
       </c>
       <c r="C71" s="66">
@@ -2670,8 +2645,8 @@
       <c r="E71" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F71" s="77" t="s">
-        <v>103</v>
+      <c r="F71" s="54" t="s">
+        <v>100</v>
       </c>
       <c r="G71" s="31">
         <v>99.35</v>
@@ -2681,15 +2656,15 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A72" s="64"/>
-      <c r="B72" s="64"/>
+      <c r="A72" s="65"/>
+      <c r="B72" s="65"/>
       <c r="C72" s="66"/>
       <c r="D72" s="67"/>
       <c r="E72" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F72" s="77" t="s">
-        <v>104</v>
+      <c r="F72" s="54" t="s">
+        <v>101</v>
       </c>
       <c r="G72" s="31">
         <v>99.64</v>
@@ -2699,15 +2674,15 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="64"/>
-      <c r="B73" s="64"/>
+      <c r="A73" s="65"/>
+      <c r="B73" s="65"/>
       <c r="C73" s="66"/>
       <c r="D73" s="67"/>
       <c r="E73" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F73" s="77" t="s">
-        <v>105</v>
+      <c r="F73" s="54" t="s">
+        <v>102</v>
       </c>
       <c r="G73" s="31">
         <v>99.38</v>
@@ -2717,15 +2692,15 @@
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A74" s="64"/>
-      <c r="B74" s="64"/>
+      <c r="A74" s="65"/>
+      <c r="B74" s="65"/>
       <c r="C74" s="66"/>
       <c r="D74" s="67"/>
       <c r="E74" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F74" s="77" t="s">
-        <v>106</v>
+      <c r="F74" s="54" t="s">
+        <v>103</v>
       </c>
       <c r="G74" s="33">
         <v>98.6</v>
@@ -2735,15 +2710,15 @@
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A75" s="64"/>
-      <c r="B75" s="64"/>
+      <c r="A75" s="65"/>
+      <c r="B75" s="65"/>
       <c r="C75" s="66"/>
       <c r="D75" s="67"/>
       <c r="E75" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F75" s="77" t="s">
-        <v>107</v>
+      <c r="F75" s="54" t="s">
+        <v>104</v>
       </c>
       <c r="G75" s="33">
         <v>91</v>
@@ -2753,8 +2728,8 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A76" s="64"/>
-      <c r="B76" s="64"/>
+      <c r="A76" s="65"/>
+      <c r="B76" s="65"/>
       <c r="C76" s="66">
         <v>500</v>
       </c>
@@ -2764,8 +2739,8 @@
       <c r="E76" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F76" s="77" t="s">
-        <v>108</v>
+      <c r="F76" s="54" t="s">
+        <v>105</v>
       </c>
       <c r="G76" s="31">
         <v>497.95</v>
@@ -2775,15 +2750,15 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A77" s="64"/>
-      <c r="B77" s="64"/>
+      <c r="A77" s="65"/>
+      <c r="B77" s="65"/>
       <c r="C77" s="66"/>
       <c r="D77" s="67"/>
       <c r="E77" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F77" s="77" t="s">
-        <v>109</v>
+      <c r="F77" s="54" t="s">
+        <v>106</v>
       </c>
       <c r="G77" s="33">
         <v>499.4</v>
@@ -2793,15 +2768,15 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A78" s="64"/>
-      <c r="B78" s="64"/>
+      <c r="A78" s="65"/>
+      <c r="B78" s="65"/>
       <c r="C78" s="66"/>
       <c r="D78" s="67"/>
       <c r="E78" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F78" s="77" t="s">
-        <v>110</v>
+      <c r="F78" s="54" t="s">
+        <v>107</v>
       </c>
       <c r="G78" s="33">
         <v>498.9</v>
@@ -2811,15 +2786,15 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A79" s="64"/>
-      <c r="B79" s="64"/>
+      <c r="A79" s="65"/>
+      <c r="B79" s="65"/>
       <c r="C79" s="66"/>
       <c r="D79" s="67"/>
       <c r="E79" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F79" s="77" t="s">
-        <v>111</v>
+      <c r="F79" s="54" t="s">
+        <v>108</v>
       </c>
       <c r="G79" s="33">
         <v>496.2</v>
@@ -2829,15 +2804,15 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A80" s="64"/>
-      <c r="B80" s="64"/>
+      <c r="A80" s="65"/>
+      <c r="B80" s="65"/>
       <c r="C80" s="66"/>
       <c r="D80" s="67"/>
       <c r="E80" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F80" s="77" t="s">
-        <v>112</v>
+      <c r="F80" s="54" t="s">
+        <v>109</v>
       </c>
       <c r="G80" s="33">
         <v>475</v>
@@ -2847,8 +2822,8 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A81" s="64"/>
-      <c r="B81" s="64"/>
+      <c r="A81" s="65"/>
+      <c r="B81" s="65"/>
       <c r="C81" s="66">
         <v>1</v>
       </c>
@@ -2858,8 +2833,8 @@
       <c r="E81" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F81" s="77" t="s">
-        <v>113</v>
+      <c r="F81" s="54" t="s">
+        <v>110</v>
       </c>
       <c r="G81" s="31">
         <v>0.99619999999999997</v>
@@ -2869,15 +2844,15 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="64"/>
-      <c r="B82" s="64"/>
+      <c r="A82" s="65"/>
+      <c r="B82" s="65"/>
       <c r="C82" s="66"/>
       <c r="D82" s="67"/>
       <c r="E82" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F82" s="77" t="s">
-        <v>114</v>
+      <c r="F82" s="54" t="s">
+        <v>111</v>
       </c>
       <c r="G82" s="31">
         <v>0.99909999999999999</v>
@@ -2887,15 +2862,15 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A83" s="64"/>
-      <c r="B83" s="64"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="65"/>
       <c r="C83" s="66"/>
       <c r="D83" s="67"/>
       <c r="E83" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F83" s="77" t="s">
-        <v>115</v>
+      <c r="F83" s="54" t="s">
+        <v>112</v>
       </c>
       <c r="G83" s="31">
         <v>0.99829999999999997</v>
@@ -2905,15 +2880,15 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A84" s="64"/>
-      <c r="B84" s="64"/>
+      <c r="A84" s="65"/>
+      <c r="B84" s="65"/>
       <c r="C84" s="66"/>
       <c r="D84" s="67"/>
       <c r="E84" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F84" s="77" t="s">
-        <v>116</v>
+      <c r="F84" s="54" t="s">
+        <v>113</v>
       </c>
       <c r="G84" s="31">
         <v>0.99319999999999997</v>
@@ -2923,15 +2898,15 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A85" s="64"/>
-      <c r="B85" s="64"/>
+      <c r="A85" s="65"/>
+      <c r="B85" s="65"/>
       <c r="C85" s="66"/>
       <c r="D85" s="67"/>
       <c r="E85" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F85" s="77" t="s">
-        <v>117</v>
+      <c r="F85" s="54" t="s">
+        <v>114</v>
       </c>
       <c r="G85" s="31">
         <v>0.95499999999999996</v>
@@ -2944,20 +2919,20 @@
       <c r="A86" s="67">
         <v>10</v>
       </c>
-      <c r="B86" s="64" t="s">
+      <c r="B86" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="C86" s="63">
+      <c r="C86" s="70">
         <v>1</v>
       </c>
-      <c r="D86" s="59" t="s">
+      <c r="D86" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E86" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F86" s="77" t="s">
-        <v>118</v>
+      <c r="F86" s="54" t="s">
+        <v>115</v>
       </c>
       <c r="G86" s="35">
         <v>0.99350000000000005</v>
@@ -2968,14 +2943,14 @@
     </row>
     <row r="87" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A87" s="67"/>
-      <c r="B87" s="64"/>
-      <c r="C87" s="63"/>
-      <c r="D87" s="59"/>
+      <c r="B87" s="65"/>
+      <c r="C87" s="70"/>
+      <c r="D87" s="68"/>
       <c r="E87" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F87" s="77" t="s">
-        <v>119</v>
+      <c r="F87" s="54" t="s">
+        <v>116</v>
       </c>
       <c r="G87" s="35">
         <v>0.99639999999999995</v>
@@ -2986,14 +2961,14 @@
     </row>
     <row r="88" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A88" s="67"/>
-      <c r="B88" s="64"/>
-      <c r="C88" s="63"/>
-      <c r="D88" s="59"/>
+      <c r="B88" s="65"/>
+      <c r="C88" s="70"/>
+      <c r="D88" s="68"/>
       <c r="E88" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F88" s="77" t="s">
-        <v>120</v>
+      <c r="F88" s="54" t="s">
+        <v>117</v>
       </c>
       <c r="G88" s="35">
         <v>0.99380000000000002</v>
@@ -3004,14 +2979,14 @@
     </row>
     <row r="89" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A89" s="67"/>
-      <c r="B89" s="64"/>
-      <c r="C89" s="63"/>
-      <c r="D89" s="59"/>
+      <c r="B89" s="65"/>
+      <c r="C89" s="70"/>
+      <c r="D89" s="68"/>
       <c r="E89" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="77" t="s">
-        <v>121</v>
+      <c r="F89" s="54" t="s">
+        <v>118</v>
       </c>
       <c r="G89" s="35">
         <v>0.98599999999999999</v>
@@ -3022,18 +2997,18 @@
     </row>
     <row r="90" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A90" s="67"/>
-      <c r="B90" s="64"/>
-      <c r="C90" s="63">
+      <c r="B90" s="65"/>
+      <c r="C90" s="70">
         <v>5</v>
       </c>
-      <c r="D90" s="59" t="s">
+      <c r="D90" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E90" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="77" t="s">
-        <v>122</v>
+      <c r="F90" s="54" t="s">
+        <v>119</v>
       </c>
       <c r="G90" s="35">
         <v>4.9794999999999998</v>
@@ -3044,14 +3019,14 @@
     </row>
     <row r="91" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A91" s="67"/>
-      <c r="B91" s="64"/>
-      <c r="C91" s="63"/>
-      <c r="D91" s="59"/>
+      <c r="B91" s="65"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="68"/>
       <c r="E91" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F91" s="77" t="s">
-        <v>123</v>
+      <c r="F91" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="G91" s="35">
         <v>4.9939999999999998</v>
@@ -3062,14 +3037,14 @@
     </row>
     <row r="92" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A92" s="67"/>
-      <c r="B92" s="64"/>
-      <c r="C92" s="63"/>
-      <c r="D92" s="59"/>
+      <c r="B92" s="65"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="68"/>
       <c r="E92" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F92" s="77" t="s">
-        <v>124</v>
+      <c r="F92" s="54" t="s">
+        <v>121</v>
       </c>
       <c r="G92" s="35">
         <v>4.9889999999999999</v>
@@ -3080,14 +3055,14 @@
     </row>
     <row r="93" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A93" s="67"/>
-      <c r="B93" s="64"/>
-      <c r="C93" s="63"/>
-      <c r="D93" s="59"/>
+      <c r="B93" s="65"/>
+      <c r="C93" s="70"/>
+      <c r="D93" s="68"/>
       <c r="E93" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F93" s="77" t="s">
-        <v>125</v>
+      <c r="F93" s="54" t="s">
+        <v>122</v>
       </c>
       <c r="G93" s="35">
         <v>4.9619999999999997</v>
@@ -3098,18 +3073,18 @@
     </row>
     <row r="94" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A94" s="67"/>
-      <c r="B94" s="64"/>
-      <c r="C94" s="63">
+      <c r="B94" s="65"/>
+      <c r="C94" s="70">
         <v>10</v>
       </c>
-      <c r="D94" s="59" t="s">
+      <c r="D94" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E94" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F94" s="77" t="s">
-        <v>126</v>
+      <c r="F94" s="54" t="s">
+        <v>123</v>
       </c>
       <c r="G94" s="35">
         <v>9.9619999999999997</v>
@@ -3120,14 +3095,14 @@
     </row>
     <row r="95" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A95" s="67"/>
-      <c r="B95" s="64"/>
-      <c r="C95" s="63"/>
-      <c r="D95" s="59"/>
+      <c r="B95" s="65"/>
+      <c r="C95" s="70"/>
+      <c r="D95" s="68"/>
       <c r="E95" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F95" s="77" t="s">
-        <v>127</v>
+      <c r="F95" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="G95" s="35">
         <v>9.9909999999999997</v>
@@ -3138,14 +3113,14 @@
     </row>
     <row r="96" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A96" s="67"/>
-      <c r="B96" s="64"/>
-      <c r="C96" s="63"/>
-      <c r="D96" s="59"/>
+      <c r="B96" s="65"/>
+      <c r="C96" s="70"/>
+      <c r="D96" s="68"/>
       <c r="E96" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F96" s="77" t="s">
-        <v>128</v>
+      <c r="F96" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="G96" s="35">
         <v>9.9830000000000005</v>
@@ -3156,14 +3131,14 @@
     </row>
     <row r="97" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A97" s="67"/>
-      <c r="B97" s="64"/>
-      <c r="C97" s="63"/>
-      <c r="D97" s="59"/>
+      <c r="B97" s="65"/>
+      <c r="C97" s="70"/>
+      <c r="D97" s="68"/>
       <c r="E97" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F97" s="77" t="s">
-        <v>129</v>
+      <c r="F97" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="G97" s="35">
         <v>9.9320000000000004</v>
@@ -3173,23 +3148,23 @@
       </c>
     </row>
     <row r="98" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A98" s="59">
+      <c r="A98" s="68">
         <v>100</v>
       </c>
-      <c r="B98" s="57" t="s">
+      <c r="B98" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="C98" s="63">
+      <c r="C98" s="70">
         <v>10</v>
       </c>
-      <c r="D98" s="59" t="s">
+      <c r="D98" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E98" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F98" s="77" t="s">
-        <v>130</v>
+      <c r="F98" s="54" t="s">
+        <v>127</v>
       </c>
       <c r="G98" s="35">
         <v>9.9350000000000005</v>
@@ -3199,15 +3174,15 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A99" s="59"/>
-      <c r="B99" s="57"/>
-      <c r="C99" s="63"/>
-      <c r="D99" s="59"/>
+      <c r="A99" s="68"/>
+      <c r="B99" s="69"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="68"/>
       <c r="E99" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F99" s="77" t="s">
-        <v>131</v>
+      <c r="F99" s="54" t="s">
+        <v>128</v>
       </c>
       <c r="G99" s="35">
         <v>9.9640000000000004</v>
@@ -3217,15 +3192,15 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A100" s="59"/>
-      <c r="B100" s="57"/>
-      <c r="C100" s="63"/>
-      <c r="D100" s="59"/>
+      <c r="A100" s="68"/>
+      <c r="B100" s="69"/>
+      <c r="C100" s="70"/>
+      <c r="D100" s="68"/>
       <c r="E100" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F100" s="77" t="s">
-        <v>132</v>
+      <c r="F100" s="54" t="s">
+        <v>129</v>
       </c>
       <c r="G100" s="35">
         <v>9.9380000000000006</v>
@@ -3235,15 +3210,15 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A101" s="59"/>
-      <c r="B101" s="57"/>
-      <c r="C101" s="63"/>
-      <c r="D101" s="59"/>
+      <c r="A101" s="68"/>
+      <c r="B101" s="69"/>
+      <c r="C101" s="70"/>
+      <c r="D101" s="68"/>
       <c r="E101" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F101" s="77" t="s">
-        <v>133</v>
+      <c r="F101" s="54" t="s">
+        <v>130</v>
       </c>
       <c r="G101" s="35">
         <v>9.86</v>
@@ -3253,19 +3228,19 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A102" s="59"/>
-      <c r="B102" s="57"/>
-      <c r="C102" s="63">
+      <c r="A102" s="68"/>
+      <c r="B102" s="69"/>
+      <c r="C102" s="70">
         <v>30</v>
       </c>
-      <c r="D102" s="59" t="s">
+      <c r="D102" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E102" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="F102" s="77" t="s">
-        <v>134</v>
+      <c r="F102" s="54" t="s">
+        <v>131</v>
       </c>
       <c r="G102" s="35">
         <v>29.795000000000002</v>
@@ -3275,15 +3250,15 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A103" s="59"/>
-      <c r="B103" s="57"/>
-      <c r="C103" s="63"/>
-      <c r="D103" s="59"/>
+      <c r="A103" s="68"/>
+      <c r="B103" s="69"/>
+      <c r="C103" s="70"/>
+      <c r="D103" s="68"/>
       <c r="E103" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F103" s="77" t="s">
-        <v>135</v>
+      <c r="F103" s="54" t="s">
+        <v>132</v>
       </c>
       <c r="G103" s="35">
         <v>29.94</v>
@@ -3293,15 +3268,15 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A104" s="59"/>
-      <c r="B104" s="57"/>
-      <c r="C104" s="63"/>
-      <c r="D104" s="59"/>
+      <c r="A104" s="68"/>
+      <c r="B104" s="69"/>
+      <c r="C104" s="70"/>
+      <c r="D104" s="68"/>
       <c r="E104" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F104" s="77" t="s">
-        <v>136</v>
+      <c r="F104" s="54" t="s">
+        <v>133</v>
       </c>
       <c r="G104" s="35">
         <v>29.89</v>
@@ -3311,15 +3286,15 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A105" s="59"/>
-      <c r="B105" s="57"/>
-      <c r="C105" s="63"/>
-      <c r="D105" s="59"/>
+      <c r="A105" s="68"/>
+      <c r="B105" s="69"/>
+      <c r="C105" s="70"/>
+      <c r="D105" s="68"/>
       <c r="E105" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F105" s="77" t="s">
-        <v>137</v>
+      <c r="F105" s="54" t="s">
+        <v>134</v>
       </c>
       <c r="G105" s="35">
         <v>29.62</v>
@@ -3329,19 +3304,19 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A106" s="59"/>
-      <c r="B106" s="57"/>
-      <c r="C106" s="63">
+      <c r="A106" s="68"/>
+      <c r="B106" s="69"/>
+      <c r="C106" s="70">
         <v>100</v>
       </c>
-      <c r="D106" s="59" t="s">
+      <c r="D106" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E106" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="F106" s="77" t="s">
-        <v>138</v>
+        <v>201</v>
+      </c>
+      <c r="F106" s="54" t="s">
+        <v>135</v>
       </c>
       <c r="G106" s="35">
         <v>99.62</v>
@@ -3351,15 +3326,15 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A107" s="59"/>
-      <c r="B107" s="57"/>
-      <c r="C107" s="63"/>
-      <c r="D107" s="59"/>
+      <c r="A107" s="68"/>
+      <c r="B107" s="69"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="68"/>
       <c r="E107" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F107" s="77" t="s">
-        <v>139</v>
+      <c r="F107" s="54" t="s">
+        <v>136</v>
       </c>
       <c r="G107" s="31">
         <v>99.91</v>
@@ -3369,15 +3344,15 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A108" s="59"/>
-      <c r="B108" s="57"/>
-      <c r="C108" s="63"/>
-      <c r="D108" s="59"/>
+      <c r="A108" s="68"/>
+      <c r="B108" s="69"/>
+      <c r="C108" s="70"/>
+      <c r="D108" s="68"/>
       <c r="E108" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F108" s="77" t="s">
-        <v>140</v>
+      <c r="F108" s="54" t="s">
+        <v>137</v>
       </c>
       <c r="G108" s="31">
         <v>99.83</v>
@@ -3387,15 +3362,15 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A109" s="59"/>
-      <c r="B109" s="57"/>
-      <c r="C109" s="63"/>
-      <c r="D109" s="59"/>
+      <c r="A109" s="68"/>
+      <c r="B109" s="69"/>
+      <c r="C109" s="70"/>
+      <c r="D109" s="68"/>
       <c r="E109" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F109" s="77" t="s">
-        <v>141</v>
+      <c r="F109" s="54" t="s">
+        <v>138</v>
       </c>
       <c r="G109" s="31">
         <v>99.32</v>
@@ -3405,23 +3380,23 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A110" s="57">
+      <c r="A110" s="69">
         <v>750</v>
       </c>
-      <c r="B110" s="57" t="s">
+      <c r="B110" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="C110" s="63">
+      <c r="C110" s="70">
         <v>100</v>
       </c>
-      <c r="D110" s="59" t="s">
+      <c r="D110" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E110" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="F110" s="77" t="s">
-        <v>142</v>
+        <v>201</v>
+      </c>
+      <c r="F110" s="54" t="s">
+        <v>139</v>
       </c>
       <c r="G110" s="35">
         <v>99.424999999999997</v>
@@ -3431,15 +3406,15 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A111" s="57"/>
-      <c r="B111" s="57"/>
-      <c r="C111" s="63"/>
-      <c r="D111" s="59"/>
+      <c r="A111" s="69"/>
+      <c r="B111" s="69"/>
+      <c r="C111" s="70"/>
+      <c r="D111" s="68"/>
       <c r="E111" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F111" s="77" t="s">
-        <v>143</v>
+      <c r="F111" s="54" t="s">
+        <v>140</v>
       </c>
       <c r="G111" s="31">
         <v>99.715000000000003</v>
@@ -3449,15 +3424,15 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A112" s="57"/>
-      <c r="B112" s="57"/>
-      <c r="C112" s="63"/>
-      <c r="D112" s="59"/>
+      <c r="A112" s="69"/>
+      <c r="B112" s="69"/>
+      <c r="C112" s="70"/>
+      <c r="D112" s="68"/>
       <c r="E112" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F112" s="77" t="s">
-        <v>144</v>
+      <c r="F112" s="54" t="s">
+        <v>141</v>
       </c>
       <c r="G112" s="31">
         <v>99.504999999999995</v>
@@ -3467,15 +3442,15 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A113" s="59"/>
-      <c r="B113" s="57"/>
-      <c r="C113" s="63"/>
-      <c r="D113" s="59"/>
+      <c r="A113" s="68"/>
+      <c r="B113" s="69"/>
+      <c r="C113" s="70"/>
+      <c r="D113" s="68"/>
       <c r="E113" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F113" s="77" t="s">
-        <v>145</v>
+      <c r="F113" s="54" t="s">
+        <v>142</v>
       </c>
       <c r="G113" s="33">
         <v>98.8</v>
@@ -3485,19 +3460,19 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A114" s="59"/>
-      <c r="B114" s="57"/>
-      <c r="C114" s="63">
+      <c r="A114" s="68"/>
+      <c r="B114" s="69"/>
+      <c r="C114" s="70">
         <v>500</v>
       </c>
-      <c r="D114" s="59" t="s">
+      <c r="D114" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E114" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="F114" s="77" t="s">
-        <v>146</v>
+        <v>201</v>
+      </c>
+      <c r="F114" s="54" t="s">
+        <v>143</v>
       </c>
       <c r="G114" s="35">
         <v>498.02499999999998</v>
@@ -3507,15 +3482,15 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A115" s="59"/>
-      <c r="B115" s="57"/>
-      <c r="C115" s="63"/>
-      <c r="D115" s="59"/>
+      <c r="A115" s="68"/>
+      <c r="B115" s="69"/>
+      <c r="C115" s="70"/>
+      <c r="D115" s="68"/>
       <c r="E115" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F115" s="77" t="s">
-        <v>147</v>
+      <c r="F115" s="54" t="s">
+        <v>144</v>
       </c>
       <c r="G115" s="31">
         <v>499.47500000000002</v>
@@ -3525,15 +3500,15 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A116" s="59"/>
-      <c r="B116" s="57"/>
-      <c r="C116" s="63"/>
-      <c r="D116" s="59"/>
+      <c r="A116" s="68"/>
+      <c r="B116" s="69"/>
+      <c r="C116" s="70"/>
+      <c r="D116" s="68"/>
       <c r="E116" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F116" s="77" t="s">
-        <v>148</v>
+      <c r="F116" s="54" t="s">
+        <v>145</v>
       </c>
       <c r="G116" s="31">
         <v>499.02499999999998</v>
@@ -3543,15 +3518,15 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A117" s="59"/>
-      <c r="B117" s="57"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="59"/>
+      <c r="A117" s="68"/>
+      <c r="B117" s="69"/>
+      <c r="C117" s="70"/>
+      <c r="D117" s="68"/>
       <c r="E117" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F117" s="77" t="s">
-        <v>149</v>
+      <c r="F117" s="54" t="s">
+        <v>146</v>
       </c>
       <c r="G117" s="30">
         <v>496.4</v>
@@ -3561,19 +3536,19 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A118" s="59"/>
-      <c r="B118" s="57"/>
-      <c r="C118" s="63">
+      <c r="A118" s="68"/>
+      <c r="B118" s="69"/>
+      <c r="C118" s="70">
         <v>750</v>
       </c>
-      <c r="D118" s="59" t="s">
+      <c r="D118" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E118" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="F118" s="77" t="s">
-        <v>150</v>
+        <v>201</v>
+      </c>
+      <c r="F118" s="54" t="s">
+        <v>147</v>
       </c>
       <c r="G118" s="35">
         <v>747.15</v>
@@ -3583,15 +3558,15 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A119" s="59"/>
-      <c r="B119" s="57"/>
-      <c r="C119" s="63"/>
-      <c r="D119" s="59"/>
+      <c r="A119" s="68"/>
+      <c r="B119" s="69"/>
+      <c r="C119" s="70"/>
+      <c r="D119" s="68"/>
       <c r="E119" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="F119" s="77" t="s">
-        <v>151</v>
+      <c r="F119" s="54" t="s">
+        <v>148</v>
       </c>
       <c r="G119" s="31">
         <v>749.32500000000005</v>
@@ -3601,15 +3576,15 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A120" s="59"/>
-      <c r="B120" s="57"/>
-      <c r="C120" s="63"/>
-      <c r="D120" s="59"/>
+      <c r="A120" s="68"/>
+      <c r="B120" s="69"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="68"/>
       <c r="E120" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F120" s="77" t="s">
-        <v>152</v>
+      <c r="F120" s="54" t="s">
+        <v>149</v>
       </c>
       <c r="G120" s="31">
         <v>748.72500000000002</v>
@@ -3619,15 +3594,15 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A121" s="59"/>
-      <c r="B121" s="57"/>
-      <c r="C121" s="63"/>
-      <c r="D121" s="59"/>
+      <c r="A121" s="68"/>
+      <c r="B121" s="69"/>
+      <c r="C121" s="70"/>
+      <c r="D121" s="68"/>
       <c r="E121" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F121" s="77" t="s">
-        <v>153</v>
+      <c r="F121" s="54" t="s">
+        <v>150</v>
       </c>
       <c r="G121" s="30">
         <v>744.9</v>
@@ -3648,7 +3623,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C123" s="16"/>
       <c r="D123" s="16"/>
@@ -3658,30 +3633,30 @@
       <c r="H123" s="18"/>
     </row>
     <row r="124" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="57" t="s">
+      <c r="A124" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B124" s="57"/>
-      <c r="C124" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D124" s="57"/>
-      <c r="E124" s="57" t="s">
+      <c r="B124" s="69"/>
+      <c r="C124" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D124" s="69"/>
+      <c r="E124" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="F124" s="57"/>
-      <c r="G124" s="56" t="s">
+      <c r="F124" s="69"/>
+      <c r="G124" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="56"/>
+      <c r="H124" s="72"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="57"/>
-      <c r="B125" s="57"/>
-      <c r="C125" s="57"/>
-      <c r="D125" s="57"/>
-      <c r="E125" s="57"/>
-      <c r="F125" s="57"/>
+      <c r="A125" s="69"/>
+      <c r="B125" s="69"/>
+      <c r="C125" s="69"/>
+      <c r="D125" s="69"/>
+      <c r="E125" s="69"/>
+      <c r="F125" s="69"/>
       <c r="G125" s="50" t="s">
         <v>18</v>
       </c>
@@ -3690,10 +3665,10 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A126" s="57">
+      <c r="A126" s="69">
         <v>10</v>
       </c>
-      <c r="B126" s="59" t="s">
+      <c r="B126" s="68" t="s">
         <v>6</v>
       </c>
       <c r="C126" s="17">
@@ -3702,10 +3677,10 @@
       <c r="D126" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E126" s="78" t="s">
-        <v>154</v>
-      </c>
-      <c r="F126" s="78"/>
+      <c r="E126" s="71" t="s">
+        <v>151</v>
+      </c>
+      <c r="F126" s="71"/>
       <c r="G126" s="35">
         <v>0.99750000000000005</v>
       </c>
@@ -3714,18 +3689,18 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A127" s="57"/>
-      <c r="B127" s="59"/>
+      <c r="A127" s="69"/>
+      <c r="B127" s="68"/>
       <c r="C127" s="17">
         <v>5</v>
       </c>
       <c r="D127" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E127" s="78" t="s">
-        <v>155</v>
-      </c>
-      <c r="F127" s="78"/>
+      <c r="E127" s="71" t="s">
+        <v>152</v>
+      </c>
+      <c r="F127" s="71"/>
       <c r="G127" s="35">
         <v>4.9954999999999998</v>
       </c>
@@ -3734,18 +3709,18 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A128" s="57"/>
-      <c r="B128" s="59"/>
+      <c r="A128" s="69"/>
+      <c r="B128" s="68"/>
       <c r="C128" s="17">
         <v>10</v>
       </c>
       <c r="D128" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E128" s="78" t="s">
-        <v>156</v>
-      </c>
-      <c r="F128" s="78"/>
+      <c r="E128" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="F128" s="71"/>
       <c r="G128" s="35">
         <v>9.9930000000000003</v>
       </c>
@@ -3754,10 +3729,10 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A129" s="57">
+      <c r="A129" s="69">
         <v>100</v>
       </c>
-      <c r="B129" s="59" t="s">
+      <c r="B129" s="68" t="s">
         <v>6</v>
       </c>
       <c r="C129" s="17">
@@ -3766,10 +3741,10 @@
       <c r="D129" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E129" s="78" t="s">
-        <v>157</v>
-      </c>
-      <c r="F129" s="78"/>
+      <c r="E129" s="71" t="s">
+        <v>154</v>
+      </c>
+      <c r="F129" s="71"/>
       <c r="G129" s="35">
         <v>9.99</v>
       </c>
@@ -3778,18 +3753,18 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A130" s="57"/>
-      <c r="B130" s="59"/>
+      <c r="A130" s="69"/>
+      <c r="B130" s="68"/>
       <c r="C130" s="17">
         <v>50</v>
       </c>
       <c r="D130" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E130" s="78" t="s">
-        <v>158</v>
-      </c>
-      <c r="F130" s="78"/>
+      <c r="E130" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="F130" s="71"/>
       <c r="G130" s="35">
         <v>49.97</v>
       </c>
@@ -3798,18 +3773,18 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A131" s="57"/>
-      <c r="B131" s="59"/>
+      <c r="A131" s="69"/>
+      <c r="B131" s="68"/>
       <c r="C131" s="17">
         <v>100</v>
       </c>
       <c r="D131" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E131" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="F131" s="78"/>
+      <c r="E131" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="F131" s="71"/>
       <c r="G131" s="35">
         <v>99.944999999999993</v>
       </c>
@@ -3818,10 +3793,10 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A132" s="59">
+      <c r="A132" s="68">
         <v>1</v>
       </c>
-      <c r="B132" s="59" t="s">
+      <c r="B132" s="68" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="17">
@@ -3830,10 +3805,10 @@
       <c r="D132" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="78" t="s">
-        <v>160</v>
-      </c>
-      <c r="F132" s="78"/>
+      <c r="E132" s="71" t="s">
+        <v>157</v>
+      </c>
+      <c r="F132" s="71"/>
       <c r="G132" s="35">
         <v>9.98E-2</v>
       </c>
@@ -3842,18 +3817,18 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A133" s="59"/>
-      <c r="B133" s="59"/>
+      <c r="A133" s="68"/>
+      <c r="B133" s="68"/>
       <c r="C133" s="17">
         <v>0.5</v>
       </c>
       <c r="D133" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="78" t="s">
-        <v>161</v>
-      </c>
-      <c r="F133" s="78"/>
+      <c r="E133" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="F133" s="71"/>
       <c r="G133" s="35">
         <v>0.49940000000000001</v>
       </c>
@@ -3862,18 +3837,18 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A134" s="59"/>
-      <c r="B134" s="59"/>
+      <c r="A134" s="68"/>
+      <c r="B134" s="68"/>
       <c r="C134" s="17">
         <v>1</v>
       </c>
       <c r="D134" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="78" t="s">
-        <v>162</v>
-      </c>
-      <c r="F134" s="78"/>
+      <c r="E134" s="71" t="s">
+        <v>159</v>
+      </c>
+      <c r="F134" s="71"/>
       <c r="G134" s="35">
         <v>0.99890000000000001</v>
       </c>
@@ -3882,10 +3857,10 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A135" s="59">
+      <c r="A135" s="68">
         <v>3</v>
       </c>
-      <c r="B135" s="59" t="s">
+      <c r="B135" s="68" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="17">
@@ -3894,10 +3869,10 @@
       <c r="D135" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="78" t="s">
-        <v>163</v>
-      </c>
-      <c r="F135" s="78"/>
+      <c r="E135" s="71" t="s">
+        <v>160</v>
+      </c>
+      <c r="F135" s="71"/>
       <c r="G135" s="35">
         <v>0.29903999999999997</v>
       </c>
@@ -3906,18 +3881,18 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A136" s="59"/>
-      <c r="B136" s="59"/>
+      <c r="A136" s="68"/>
+      <c r="B136" s="68"/>
       <c r="C136" s="17">
         <v>1</v>
       </c>
       <c r="D136" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="78" t="s">
-        <v>164</v>
-      </c>
-      <c r="F136" s="78"/>
+      <c r="E136" s="71" t="s">
+        <v>161</v>
+      </c>
+      <c r="F136" s="71"/>
       <c r="G136" s="35">
         <v>0.99819999999999998</v>
       </c>
@@ -3926,18 +3901,18 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A137" s="59"/>
-      <c r="B137" s="59"/>
+      <c r="A137" s="68"/>
+      <c r="B137" s="68"/>
       <c r="C137" s="17">
         <v>2.5</v>
       </c>
       <c r="D137" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="78" t="s">
-        <v>165</v>
-      </c>
-      <c r="F137" s="78"/>
+      <c r="E137" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="F137" s="71"/>
       <c r="G137" s="35">
         <v>2.4964</v>
       </c>
@@ -3950,45 +3925,45 @@
       <c r="B138" s="20"/>
       <c r="C138" s="40"/>
       <c r="D138" s="20"/>
-      <c r="E138" s="79"/>
-      <c r="F138" s="79"/>
+      <c r="E138" s="55"/>
+      <c r="F138" s="55"/>
       <c r="G138" s="22"/>
       <c r="H138" s="23"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G139" s="18"/>
       <c r="H139" s="18"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A140" s="57" t="s">
+      <c r="A140" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B140" s="57"/>
-      <c r="C140" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D140" s="57"/>
-      <c r="E140" s="57" t="s">
+      <c r="B140" s="69"/>
+      <c r="C140" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D140" s="69"/>
+      <c r="E140" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="F140" s="57" t="s">
+      <c r="F140" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="G140" s="56" t="s">
+      <c r="G140" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H140" s="56"/>
+      <c r="H140" s="72"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141" s="57"/>
-      <c r="B141" s="57"/>
-      <c r="C141" s="57"/>
-      <c r="D141" s="57"/>
-      <c r="E141" s="57"/>
-      <c r="F141" s="57"/>
+      <c r="A141" s="69"/>
+      <c r="B141" s="69"/>
+      <c r="C141" s="69"/>
+      <c r="D141" s="69"/>
+      <c r="E141" s="69"/>
+      <c r="F141" s="69"/>
       <c r="G141" s="50" t="s">
         <v>18</v>
       </c>
@@ -3997,23 +3972,23 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A142" s="57">
+      <c r="A142" s="69">
         <v>1</v>
       </c>
-      <c r="B142" s="59" t="s">
+      <c r="B142" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C142" s="59">
+      <c r="C142" s="68">
         <v>0.1</v>
       </c>
-      <c r="D142" s="59" t="s">
+      <c r="D142" s="68" t="s">
         <v>7</v>
       </c>
       <c r="E142" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F142" s="77" t="s">
-        <v>166</v>
+      <c r="F142" s="54" t="s">
+        <v>163</v>
       </c>
       <c r="G142" s="35">
         <v>9.9299999999999999E-2</v>
@@ -4023,51 +3998,51 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A143" s="57"/>
-      <c r="B143" s="59"/>
-      <c r="C143" s="59"/>
-      <c r="D143" s="59"/>
+      <c r="A143" s="69"/>
+      <c r="B143" s="68"/>
+      <c r="C143" s="68"/>
+      <c r="D143" s="68"/>
       <c r="E143" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F143" s="77" t="s">
-        <v>167</v>
-      </c>
-      <c r="G143" s="56">
+      <c r="F143" s="54" t="s">
+        <v>164</v>
+      </c>
+      <c r="G143" s="72">
         <v>9.9500000000000005E-2</v>
       </c>
-      <c r="H143" s="56">
+      <c r="H143" s="72">
         <v>0.10050000000000001</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A144" s="57"/>
-      <c r="B144" s="59"/>
-      <c r="C144" s="59"/>
-      <c r="D144" s="59"/>
+      <c r="A144" s="69"/>
+      <c r="B144" s="68"/>
+      <c r="C144" s="68"/>
+      <c r="D144" s="68"/>
       <c r="E144" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F144" s="77" t="s">
-        <v>168</v>
-      </c>
-      <c r="G144" s="56"/>
-      <c r="H144" s="56"/>
+      <c r="F144" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="G144" s="72"/>
+      <c r="H144" s="72"/>
     </row>
     <row r="145" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A145" s="57"/>
-      <c r="B145" s="59"/>
-      <c r="C145" s="59">
+      <c r="A145" s="69"/>
+      <c r="B145" s="68"/>
+      <c r="C145" s="68">
         <v>0.5</v>
       </c>
-      <c r="D145" s="59" t="s">
+      <c r="D145" s="68" t="s">
         <v>7</v>
       </c>
       <c r="E145" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F145" s="77" t="s">
-        <v>169</v>
+      <c r="F145" s="54" t="s">
+        <v>166</v>
       </c>
       <c r="G145" s="49">
         <v>0.49809999999999999</v>
@@ -4077,51 +4052,51 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A146" s="57"/>
-      <c r="B146" s="59"/>
-      <c r="C146" s="59"/>
-      <c r="D146" s="59"/>
+      <c r="A146" s="69"/>
+      <c r="B146" s="68"/>
+      <c r="C146" s="68"/>
+      <c r="D146" s="68"/>
       <c r="E146" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F146" s="77" t="s">
-        <v>170</v>
-      </c>
-      <c r="G146" s="56">
+      <c r="F146" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="G146" s="72">
         <v>0.49909999999999999</v>
       </c>
-      <c r="H146" s="56">
+      <c r="H146" s="72">
         <v>0.50090000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A147" s="57"/>
-      <c r="B147" s="59"/>
-      <c r="C147" s="59"/>
-      <c r="D147" s="59"/>
+      <c r="A147" s="69"/>
+      <c r="B147" s="68"/>
+      <c r="C147" s="68"/>
+      <c r="D147" s="68"/>
       <c r="E147" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F147" s="77" t="s">
-        <v>171</v>
-      </c>
-      <c r="G147" s="56"/>
-      <c r="H147" s="56"/>
+      <c r="F147" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="G147" s="72"/>
+      <c r="H147" s="72"/>
     </row>
     <row r="148" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A148" s="57"/>
-      <c r="B148" s="59"/>
-      <c r="C148" s="63">
+      <c r="A148" s="69"/>
+      <c r="B148" s="68"/>
+      <c r="C148" s="70">
         <v>1</v>
       </c>
-      <c r="D148" s="59" t="s">
+      <c r="D148" s="68" t="s">
         <v>7</v>
       </c>
       <c r="E148" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F148" s="77" t="s">
-        <v>172</v>
+      <c r="F148" s="54" t="s">
+        <v>169</v>
       </c>
       <c r="G148" s="49">
         <v>0.99660000000000004</v>
@@ -4131,55 +4106,55 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A149" s="57"/>
-      <c r="B149" s="59"/>
-      <c r="C149" s="63"/>
-      <c r="D149" s="59"/>
+      <c r="A149" s="69"/>
+      <c r="B149" s="68"/>
+      <c r="C149" s="70"/>
+      <c r="D149" s="68"/>
       <c r="E149" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F149" s="77" t="s">
-        <v>173</v>
-      </c>
-      <c r="G149" s="56">
+      <c r="F149" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="G149" s="72">
         <v>0.99860000000000004</v>
       </c>
-      <c r="H149" s="56">
+      <c r="H149" s="72">
         <v>1.0014000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A150" s="57"/>
-      <c r="B150" s="59"/>
-      <c r="C150" s="63"/>
-      <c r="D150" s="59"/>
+      <c r="A150" s="69"/>
+      <c r="B150" s="68"/>
+      <c r="C150" s="70"/>
+      <c r="D150" s="68"/>
       <c r="E150" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F150" s="77" t="s">
-        <v>174</v>
-      </c>
-      <c r="G150" s="56"/>
-      <c r="H150" s="56"/>
+      <c r="F150" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="G150" s="72"/>
+      <c r="H150" s="72"/>
     </row>
     <row r="151" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A151" s="57">
+      <c r="A151" s="69">
         <v>3</v>
       </c>
-      <c r="B151" s="59" t="s">
+      <c r="B151" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C151" s="63">
+      <c r="C151" s="70">
         <v>0.3</v>
       </c>
-      <c r="D151" s="59" t="s">
+      <c r="D151" s="68" t="s">
         <v>7</v>
       </c>
       <c r="E151" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F151" s="77" t="s">
-        <v>175</v>
+      <c r="F151" s="54" t="s">
+        <v>172</v>
       </c>
       <c r="G151" s="49">
         <v>0.29715000000000003</v>
@@ -4189,51 +4164,51 @@
       </c>
     </row>
     <row r="152" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A152" s="57"/>
-      <c r="B152" s="59"/>
-      <c r="C152" s="63"/>
-      <c r="D152" s="59"/>
+      <c r="A152" s="69"/>
+      <c r="B152" s="68"/>
+      <c r="C152" s="70"/>
+      <c r="D152" s="68"/>
       <c r="E152" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F152" s="77" t="s">
-        <v>176</v>
-      </c>
-      <c r="G152" s="56">
+      <c r="F152" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="G152" s="72">
         <v>0.29775000000000001</v>
       </c>
-      <c r="H152" s="56">
+      <c r="H152" s="72">
         <v>0.30225000000000002</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A153" s="57"/>
-      <c r="B153" s="59"/>
-      <c r="C153" s="63"/>
-      <c r="D153" s="59"/>
+      <c r="A153" s="69"/>
+      <c r="B153" s="68"/>
+      <c r="C153" s="70"/>
+      <c r="D153" s="68"/>
       <c r="E153" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F153" s="77" t="s">
-        <v>177</v>
-      </c>
-      <c r="G153" s="56"/>
-      <c r="H153" s="56"/>
+      <c r="F153" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="G153" s="72"/>
+      <c r="H153" s="72"/>
     </row>
     <row r="154" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A154" s="57"/>
-      <c r="B154" s="59"/>
-      <c r="C154" s="63">
+      <c r="A154" s="69"/>
+      <c r="B154" s="68"/>
+      <c r="C154" s="70">
         <v>1</v>
       </c>
-      <c r="D154" s="59" t="s">
+      <c r="D154" s="68" t="s">
         <v>7</v>
       </c>
       <c r="E154" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F154" s="77" t="s">
-        <v>178</v>
+      <c r="F154" s="54" t="s">
+        <v>175</v>
       </c>
       <c r="G154" s="49">
         <v>0.99470000000000003</v>
@@ -4243,51 +4218,51 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A155" s="57"/>
-      <c r="B155" s="59"/>
-      <c r="C155" s="63"/>
-      <c r="D155" s="59"/>
+      <c r="A155" s="69"/>
+      <c r="B155" s="68"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="68"/>
       <c r="E155" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F155" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="G155" s="56">
+      <c r="F155" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="G155" s="72">
         <v>0.99790000000000001</v>
       </c>
-      <c r="H155" s="56">
+      <c r="H155" s="72">
         <v>1.0021</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A156" s="57"/>
-      <c r="B156" s="59"/>
-      <c r="C156" s="63"/>
-      <c r="D156" s="59"/>
+      <c r="A156" s="69"/>
+      <c r="B156" s="68"/>
+      <c r="C156" s="70"/>
+      <c r="D156" s="68"/>
       <c r="E156" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F156" s="77" t="s">
-        <v>180</v>
-      </c>
-      <c r="G156" s="56"/>
-      <c r="H156" s="56"/>
+      <c r="F156" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="G156" s="72"/>
+      <c r="H156" s="72"/>
     </row>
     <row r="157" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A157" s="57"/>
-      <c r="B157" s="59"/>
-      <c r="C157" s="63">
+      <c r="A157" s="69"/>
+      <c r="B157" s="68"/>
+      <c r="C157" s="70">
         <v>2.5</v>
       </c>
-      <c r="D157" s="59" t="s">
+      <c r="D157" s="68" t="s">
         <v>7</v>
       </c>
       <c r="E157" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F157" s="77" t="s">
-        <v>181</v>
+      <c r="F157" s="54" t="s">
+        <v>178</v>
       </c>
       <c r="G157" s="49">
         <v>2.4894500000000002</v>
@@ -4297,36 +4272,36 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A158" s="57"/>
-      <c r="B158" s="59"/>
-      <c r="C158" s="63"/>
-      <c r="D158" s="59"/>
+      <c r="A158" s="69"/>
+      <c r="B158" s="68"/>
+      <c r="C158" s="70"/>
+      <c r="D158" s="68"/>
       <c r="E158" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F158" s="77" t="s">
-        <v>182</v>
-      </c>
-      <c r="G158" s="56">
+      <c r="F158" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="G158" s="72">
         <v>2.4944500000000001</v>
       </c>
-      <c r="H158" s="56">
+      <c r="H158" s="72">
         <v>2.5055499999999999</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A159" s="57"/>
-      <c r="B159" s="59"/>
-      <c r="C159" s="63"/>
-      <c r="D159" s="59"/>
+      <c r="A159" s="69"/>
+      <c r="B159" s="68"/>
+      <c r="C159" s="70"/>
+      <c r="D159" s="68"/>
       <c r="E159" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F159" s="77" t="s">
-        <v>183</v>
-      </c>
-      <c r="G159" s="56"/>
-      <c r="H159" s="56"/>
+      <c r="F159" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="G159" s="72"/>
+      <c r="H159" s="72"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="21"/>
@@ -4340,43 +4315,43 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G161" s="18"/>
       <c r="H161" s="18"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G162" s="18"/>
       <c r="H162" s="18"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163" s="57" t="s">
+      <c r="A163" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B163" s="57"/>
-      <c r="C163" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D163" s="57"/>
-      <c r="E163" s="57" t="s">
+      <c r="B163" s="69"/>
+      <c r="C163" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D163" s="69"/>
+      <c r="E163" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F163" s="57"/>
-      <c r="G163" s="56" t="s">
+      <c r="F163" s="69"/>
+      <c r="G163" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H163" s="56"/>
+      <c r="H163" s="72"/>
     </row>
     <row r="164" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="57"/>
-      <c r="B164" s="57"/>
-      <c r="C164" s="57"/>
-      <c r="D164" s="57"/>
-      <c r="E164" s="57"/>
-      <c r="F164" s="57"/>
+      <c r="A164" s="69"/>
+      <c r="B164" s="69"/>
+      <c r="C164" s="69"/>
+      <c r="D164" s="69"/>
+      <c r="E164" s="69"/>
+      <c r="F164" s="69"/>
       <c r="G164" s="50" t="s">
         <v>18</v>
       </c>
@@ -4385,10 +4360,10 @@
       </c>
     </row>
     <row r="165" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A165" s="57">
+      <c r="A165" s="69">
         <v>100</v>
       </c>
-      <c r="B165" s="59" t="s">
+      <c r="B165" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C165" s="17">
@@ -4397,10 +4372,10 @@
       <c r="D165" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="E165" s="78" t="s">
-        <v>207</v>
-      </c>
-      <c r="F165" s="78"/>
+      <c r="E165" s="71" t="s">
+        <v>204</v>
+      </c>
+      <c r="F165" s="71"/>
       <c r="G165" s="35">
         <v>9.9949999999999992</v>
       </c>
@@ -4409,18 +4384,18 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A166" s="57"/>
-      <c r="B166" s="59"/>
+      <c r="A166" s="69"/>
+      <c r="B166" s="68"/>
       <c r="C166" s="17">
         <v>50</v>
       </c>
       <c r="D166" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="E166" s="78" t="s">
-        <v>208</v>
-      </c>
-      <c r="F166" s="78"/>
+      <c r="E166" s="71" t="s">
+        <v>205</v>
+      </c>
+      <c r="F166" s="71"/>
       <c r="G166" s="35">
         <v>49.991</v>
       </c>
@@ -4429,18 +4404,18 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A167" s="57"/>
-      <c r="B167" s="59"/>
+      <c r="A167" s="69"/>
+      <c r="B167" s="68"/>
       <c r="C167" s="17">
         <v>100</v>
       </c>
       <c r="D167" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="E167" s="78" t="s">
-        <v>209</v>
-      </c>
-      <c r="F167" s="78"/>
+      <c r="E167" s="71" t="s">
+        <v>206</v>
+      </c>
+      <c r="F167" s="71"/>
       <c r="G167" s="35">
         <v>99.986000000000004</v>
       </c>
@@ -4449,10 +4424,10 @@
       </c>
     </row>
     <row r="168" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A168" s="57">
+      <c r="A168" s="69">
         <v>1</v>
       </c>
-      <c r="B168" s="59" t="s">
+      <c r="B168" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C168" s="36">
@@ -4461,10 +4436,10 @@
       <c r="D168" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E168" s="78" t="s">
-        <v>210</v>
-      </c>
-      <c r="F168" s="78"/>
+      <c r="E168" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="F168" s="71"/>
       <c r="G168" s="35">
         <v>9.9979999999999999E-2</v>
       </c>
@@ -4473,18 +4448,18 @@
       </c>
     </row>
     <row r="169" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A169" s="57"/>
-      <c r="B169" s="59"/>
+      <c r="A169" s="69"/>
+      <c r="B169" s="68"/>
       <c r="C169" s="17">
         <v>0.5</v>
       </c>
       <c r="D169" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E169" s="78" t="s">
-        <v>211</v>
-      </c>
-      <c r="F169" s="78"/>
+      <c r="E169" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="F169" s="71"/>
       <c r="G169" s="35">
         <v>0.49994</v>
       </c>
@@ -4493,18 +4468,18 @@
       </c>
     </row>
     <row r="170" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A170" s="57"/>
-      <c r="B170" s="59"/>
+      <c r="A170" s="69"/>
+      <c r="B170" s="68"/>
       <c r="C170" s="17">
         <v>1</v>
       </c>
       <c r="D170" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E170" s="78" t="s">
-        <v>212</v>
-      </c>
-      <c r="F170" s="78"/>
+      <c r="E170" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="F170" s="71"/>
       <c r="G170" s="35">
         <v>0.99988999999999995</v>
       </c>
@@ -4514,41 +4489,41 @@
     </row>
     <row r="171" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A171" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B171" s="20"/>
       <c r="C171" s="40"/>
       <c r="D171" s="20"/>
-      <c r="E171" s="80"/>
-      <c r="F171" s="80"/>
+      <c r="E171" s="56"/>
+      <c r="F171" s="56"/>
       <c r="G171" s="22"/>
       <c r="H171" s="23"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A172" s="57" t="s">
+      <c r="A172" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B172" s="57"/>
-      <c r="C172" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D172" s="57"/>
-      <c r="E172" s="57" t="s">
+      <c r="B172" s="69"/>
+      <c r="C172" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D172" s="69"/>
+      <c r="E172" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F172" s="57"/>
-      <c r="G172" s="56" t="s">
+      <c r="F172" s="69"/>
+      <c r="G172" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H172" s="56"/>
+      <c r="H172" s="72"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A173" s="57"/>
-      <c r="B173" s="57"/>
-      <c r="C173" s="57"/>
-      <c r="D173" s="57"/>
-      <c r="E173" s="57"/>
-      <c r="F173" s="57"/>
+      <c r="A173" s="69"/>
+      <c r="B173" s="69"/>
+      <c r="C173" s="69"/>
+      <c r="D173" s="69"/>
+      <c r="E173" s="69"/>
+      <c r="F173" s="69"/>
       <c r="G173" s="50" t="s">
         <v>18</v>
       </c>
@@ -4557,10 +4532,10 @@
       </c>
     </row>
     <row r="174" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A174" s="59">
+      <c r="A174" s="68">
         <v>10</v>
       </c>
-      <c r="B174" s="59" t="s">
+      <c r="B174" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C174" s="36">
@@ -4569,10 +4544,10 @@
       <c r="D174" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E174" s="78" t="s">
-        <v>187</v>
-      </c>
-      <c r="F174" s="78"/>
+      <c r="E174" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="F174" s="71"/>
       <c r="G174" s="35">
         <v>0.99980000000000002</v>
       </c>
@@ -4581,18 +4556,18 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A175" s="59"/>
-      <c r="B175" s="59"/>
+      <c r="A175" s="68"/>
+      <c r="B175" s="68"/>
       <c r="C175" s="17">
         <v>5</v>
       </c>
       <c r="D175" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E175" s="78" t="s">
-        <v>188</v>
-      </c>
-      <c r="F175" s="78"/>
+      <c r="E175" s="71" t="s">
+        <v>185</v>
+      </c>
+      <c r="F175" s="71"/>
       <c r="G175" s="35">
         <v>4.9993999999999996</v>
       </c>
@@ -4601,18 +4576,18 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A176" s="59"/>
-      <c r="B176" s="59"/>
+      <c r="A176" s="68"/>
+      <c r="B176" s="68"/>
       <c r="C176" s="17">
         <v>10</v>
       </c>
       <c r="D176" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E176" s="78" t="s">
-        <v>189</v>
-      </c>
-      <c r="F176" s="78"/>
+      <c r="E176" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="F176" s="71"/>
       <c r="G176" s="35">
         <v>9.9989000000000008</v>
       </c>
@@ -4621,10 +4596,10 @@
       </c>
     </row>
     <row r="177" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A177" s="59">
+      <c r="A177" s="68">
         <v>100</v>
       </c>
-      <c r="B177" s="59" t="s">
+      <c r="B177" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C177" s="17">
@@ -4633,10 +4608,10 @@
       <c r="D177" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E177" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="F177" s="78"/>
+      <c r="E177" s="71" t="s">
+        <v>187</v>
+      </c>
+      <c r="F177" s="71"/>
       <c r="G177" s="35">
         <v>9.9979999999999993</v>
       </c>
@@ -4645,18 +4620,18 @@
       </c>
     </row>
     <row r="178" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A178" s="59"/>
-      <c r="B178" s="59"/>
+      <c r="A178" s="68"/>
+      <c r="B178" s="68"/>
       <c r="C178" s="17">
         <v>50</v>
       </c>
       <c r="D178" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E178" s="78" t="s">
-        <v>191</v>
-      </c>
-      <c r="F178" s="78"/>
+      <c r="E178" s="71" t="s">
+        <v>188</v>
+      </c>
+      <c r="F178" s="71"/>
       <c r="G178" s="35">
         <v>49.994</v>
       </c>
@@ -4665,18 +4640,18 @@
       </c>
     </row>
     <row r="179" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A179" s="59"/>
-      <c r="B179" s="59"/>
+      <c r="A179" s="68"/>
+      <c r="B179" s="68"/>
       <c r="C179" s="17">
         <v>100</v>
       </c>
       <c r="D179" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E179" s="78" t="s">
-        <v>192</v>
-      </c>
-      <c r="F179" s="78"/>
+      <c r="E179" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="F179" s="71"/>
       <c r="G179" s="35">
         <v>99.989000000000004</v>
       </c>
@@ -4685,10 +4660,10 @@
       </c>
     </row>
     <row r="180" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A180" s="57">
+      <c r="A180" s="69">
         <v>1</v>
       </c>
-      <c r="B180" s="59" t="s">
+      <c r="B180" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C180" s="17">
@@ -4697,10 +4672,10 @@
       <c r="D180" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E180" s="78" t="s">
-        <v>193</v>
-      </c>
-      <c r="F180" s="78"/>
+      <c r="E180" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="F180" s="71"/>
       <c r="G180" s="35">
         <v>9.9979999999999999E-2</v>
       </c>
@@ -4709,18 +4684,18 @@
       </c>
     </row>
     <row r="181" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A181" s="59"/>
-      <c r="B181" s="59"/>
+      <c r="A181" s="68"/>
+      <c r="B181" s="68"/>
       <c r="C181" s="17">
         <v>0.5</v>
       </c>
       <c r="D181" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E181" s="78" t="s">
-        <v>194</v>
-      </c>
-      <c r="F181" s="78"/>
+      <c r="E181" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="F181" s="71"/>
       <c r="G181" s="35">
         <v>0.49994</v>
       </c>
@@ -4729,18 +4704,18 @@
       </c>
     </row>
     <row r="182" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A182" s="58"/>
-      <c r="B182" s="58"/>
+      <c r="A182" s="60"/>
+      <c r="B182" s="60"/>
       <c r="C182" s="36">
         <v>1</v>
       </c>
       <c r="D182" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E182" s="78" t="s">
-        <v>195</v>
-      </c>
-      <c r="F182" s="78"/>
+      <c r="E182" s="71" t="s">
+        <v>192</v>
+      </c>
+      <c r="F182" s="71"/>
       <c r="G182" s="35">
         <v>0.99988999999999995</v>
       </c>
@@ -4749,10 +4724,10 @@
       </c>
     </row>
     <row r="183" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A183" s="59">
+      <c r="A183" s="68">
         <v>10</v>
       </c>
-      <c r="B183" s="59" t="s">
+      <c r="B183" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C183" s="36">
@@ -4761,10 +4736,10 @@
       <c r="D183" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E183" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="F183" s="78"/>
+      <c r="E183" s="71" t="s">
+        <v>193</v>
+      </c>
+      <c r="F183" s="71"/>
       <c r="G183" s="35">
         <v>0.99950000000000006</v>
       </c>
@@ -4773,18 +4748,18 @@
       </c>
     </row>
     <row r="184" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A184" s="59"/>
-      <c r="B184" s="59"/>
+      <c r="A184" s="68"/>
+      <c r="B184" s="68"/>
       <c r="C184" s="36">
         <v>5</v>
       </c>
       <c r="D184" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E184" s="78" t="s">
-        <v>197</v>
-      </c>
-      <c r="F184" s="78"/>
+      <c r="E184" s="71" t="s">
+        <v>194</v>
+      </c>
+      <c r="F184" s="71"/>
       <c r="G184" s="35">
         <v>4.9978999999999996</v>
       </c>
@@ -4793,18 +4768,18 @@
       </c>
     </row>
     <row r="185" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A185" s="59"/>
-      <c r="B185" s="59"/>
+      <c r="A185" s="68"/>
+      <c r="B185" s="68"/>
       <c r="C185" s="36">
         <v>10</v>
       </c>
       <c r="D185" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E185" s="78" t="s">
-        <v>198</v>
-      </c>
-      <c r="F185" s="78"/>
+      <c r="E185" s="71" t="s">
+        <v>195</v>
+      </c>
+      <c r="F185" s="71"/>
       <c r="G185" s="35">
         <v>9.9959000000000007</v>
       </c>
@@ -4813,10 +4788,10 @@
       </c>
     </row>
     <row r="186" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A186" s="59">
+      <c r="A186" s="68">
         <v>100</v>
       </c>
-      <c r="B186" s="59" t="s">
+      <c r="B186" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C186" s="36">
@@ -4825,10 +4800,10 @@
       <c r="D186" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E186" s="78" t="s">
-        <v>199</v>
-      </c>
-      <c r="F186" s="78"/>
+      <c r="E186" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="F186" s="71"/>
       <c r="G186" s="35">
         <v>9.91</v>
       </c>
@@ -4837,18 +4812,18 @@
       </c>
     </row>
     <row r="187" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A187" s="59"/>
-      <c r="B187" s="59"/>
+      <c r="A187" s="68"/>
+      <c r="B187" s="68"/>
       <c r="C187" s="36">
         <v>50</v>
       </c>
       <c r="D187" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E187" s="78" t="s">
-        <v>200</v>
-      </c>
-      <c r="F187" s="78"/>
+      <c r="E187" s="71" t="s">
+        <v>197</v>
+      </c>
+      <c r="F187" s="71"/>
       <c r="G187" s="35">
         <v>49.59</v>
       </c>
@@ -4857,18 +4832,18 @@
       </c>
     </row>
     <row r="188" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A188" s="59"/>
-      <c r="B188" s="59"/>
+      <c r="A188" s="68"/>
+      <c r="B188" s="68"/>
       <c r="C188" s="36">
         <v>100</v>
       </c>
       <c r="D188" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E188" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="F188" s="78"/>
+      <c r="E188" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="F188" s="71"/>
       <c r="G188" s="35">
         <v>99.19</v>
       </c>
@@ -4888,7 +4863,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B190" s="20"/>
       <c r="C190" s="28"/>
@@ -4899,25 +4874,25 @@
       <c r="H190" s="24"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A191" s="60" t="s">
+      <c r="A191" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B191" s="60"/>
-      <c r="C191" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D191" s="57"/>
-      <c r="E191" s="61" t="s">
+      <c r="B191" s="78"/>
+      <c r="C191" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D191" s="69"/>
+      <c r="E191" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="F191" s="61"/>
+      <c r="F191" s="79"/>
       <c r="G191" s="10"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A192" s="60"/>
-      <c r="B192" s="60"/>
-      <c r="C192" s="57"/>
-      <c r="D192" s="57"/>
+      <c r="A192" s="78"/>
+      <c r="B192" s="78"/>
+      <c r="C192" s="69"/>
+      <c r="D192" s="69"/>
       <c r="E192" s="50" t="s">
         <v>18</v>
       </c>
@@ -4931,12 +4906,12 @@
         <v>10</v>
       </c>
       <c r="B193" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="C193" s="76" t="s">
-        <v>184</v>
-      </c>
-      <c r="D193" s="76"/>
+        <v>199</v>
+      </c>
+      <c r="C193" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="D193" s="73"/>
       <c r="E193" s="47">
         <v>9.9949999999999992</v>
       </c>
@@ -4949,13 +4924,13 @@
       <c r="A194" s="45">
         <v>50</v>
       </c>
-      <c r="B194" s="52" t="s">
-        <v>203</v>
-      </c>
-      <c r="C194" s="76" t="s">
-        <v>185</v>
-      </c>
-      <c r="D194" s="76"/>
+      <c r="B194" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="C194" s="73" t="s">
+        <v>182</v>
+      </c>
+      <c r="D194" s="73"/>
       <c r="E194" s="47">
         <v>49.984999999999999</v>
       </c>
@@ -4968,11 +4943,11 @@
       <c r="A195" s="45">
         <v>300</v>
       </c>
-      <c r="B195" s="53"/>
-      <c r="C195" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="D195" s="76"/>
+      <c r="B195" s="81"/>
+      <c r="C195" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="D195" s="73"/>
       <c r="E195" s="47">
         <v>299.97000000000003</v>
       </c>
@@ -4986,13 +4961,13 @@
       <c r="G196" s="16"/>
       <c r="H196" s="24"/>
     </row>
-    <row r="197" spans="1:8" s="81" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A197" s="54" t="s">
-        <v>217</v>
-      </c>
-      <c r="B197" s="54"/>
+    <row r="197" spans="1:8" s="57" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A197" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="B197" s="76"/>
       <c r="C197" s="43" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D197" s="16"/>
       <c r="E197" s="16"/>
@@ -5000,33 +4975,33 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="1:8" s="81" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A198" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="B198" s="54"/>
+    <row r="198" spans="1:8" s="57" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A198" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="B198" s="76"/>
       <c r="C198" s="37"/>
       <c r="D198" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E198" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="F198" s="83"/>
+      <c r="G198" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H198" s="39"/>
+    </row>
+    <row r="199" spans="1:8" s="57" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A199" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="E198" s="82" t="s">
+      <c r="B199" s="76"/>
+      <c r="C199" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="F198" s="55"/>
-      <c r="G198" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H198" s="39"/>
-    </row>
-    <row r="199" spans="1:8" s="81" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A199" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B199" s="54"/>
-      <c r="C199" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="D199" s="83"/>
+      <c r="D199" s="77"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
@@ -5034,62 +5009,151 @@
     </row>
   </sheetData>
   <mergeCells count="225">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="B71:B85"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
-    <mergeCell ref="C76:C80"/>
-    <mergeCell ref="D76:D80"/>
-    <mergeCell ref="C81:C85"/>
-    <mergeCell ref="D81:D85"/>
-    <mergeCell ref="A98:A109"/>
-    <mergeCell ref="B98:B109"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="A86:A97"/>
-    <mergeCell ref="B86:B97"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="A198:B198"/>
+    <mergeCell ref="E198:F198"/>
+    <mergeCell ref="G124:H124"/>
+    <mergeCell ref="H158:H159"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="H152:H153"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="A197:B197"/>
+    <mergeCell ref="E140:E141"/>
+    <mergeCell ref="F140:F141"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="G155:G156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="A151:A159"/>
+    <mergeCell ref="A199:B199"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="A55:B56"/>
+    <mergeCell ref="G158:G159"/>
+    <mergeCell ref="A191:B192"/>
+    <mergeCell ref="C191:D192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="E191:F191"/>
+    <mergeCell ref="A57:A70"/>
+    <mergeCell ref="B57:B70"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="D57:D60"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="A110:A121"/>
+    <mergeCell ref="B110:B121"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="B126:B128"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="E124:F125"/>
+    <mergeCell ref="A71:A85"/>
+    <mergeCell ref="B151:B159"/>
+    <mergeCell ref="C154:C156"/>
+    <mergeCell ref="D154:D156"/>
+    <mergeCell ref="C157:C159"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="A132:A134"/>
+    <mergeCell ref="B132:B134"/>
+    <mergeCell ref="A135:A137"/>
+    <mergeCell ref="B135:B137"/>
+    <mergeCell ref="B142:B150"/>
+    <mergeCell ref="C142:C144"/>
+    <mergeCell ref="D142:D144"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="C32:D33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="E32:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A186:A188"/>
+    <mergeCell ref="B186:B188"/>
+    <mergeCell ref="A183:A185"/>
+    <mergeCell ref="B183:B185"/>
+    <mergeCell ref="E183:F183"/>
+    <mergeCell ref="E185:F185"/>
+    <mergeCell ref="E184:F184"/>
+    <mergeCell ref="A180:A182"/>
+    <mergeCell ref="A142:A150"/>
+    <mergeCell ref="A177:A179"/>
+    <mergeCell ref="B177:B179"/>
+    <mergeCell ref="E177:F177"/>
+    <mergeCell ref="E178:F178"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="B180:B182"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="E181:F181"/>
+    <mergeCell ref="E182:F182"/>
+    <mergeCell ref="A168:A170"/>
+    <mergeCell ref="B168:B170"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="A174:A176"/>
+    <mergeCell ref="B174:B176"/>
+    <mergeCell ref="E174:F174"/>
+    <mergeCell ref="E175:F175"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="B165:B167"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="G172:H172"/>
     <mergeCell ref="E186:F186"/>
     <mergeCell ref="E188:F188"/>
     <mergeCell ref="E187:F187"/>
@@ -5114,151 +5178,62 @@
     <mergeCell ref="C148:C150"/>
     <mergeCell ref="D148:D150"/>
     <mergeCell ref="C151:C153"/>
-    <mergeCell ref="B174:B176"/>
-    <mergeCell ref="E174:F174"/>
-    <mergeCell ref="E175:F175"/>
-    <mergeCell ref="E176:F176"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="B165:B167"/>
-    <mergeCell ref="E165:F165"/>
-    <mergeCell ref="E166:F166"/>
-    <mergeCell ref="E167:F167"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="A186:A188"/>
-    <mergeCell ref="B186:B188"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="B183:B185"/>
-    <mergeCell ref="E183:F183"/>
-    <mergeCell ref="E185:F185"/>
-    <mergeCell ref="E184:F184"/>
-    <mergeCell ref="A180:A182"/>
-    <mergeCell ref="A142:A150"/>
-    <mergeCell ref="A177:A179"/>
-    <mergeCell ref="B177:B179"/>
-    <mergeCell ref="E177:F177"/>
-    <mergeCell ref="E178:F178"/>
-    <mergeCell ref="E179:F179"/>
-    <mergeCell ref="B180:B182"/>
-    <mergeCell ref="E180:F180"/>
-    <mergeCell ref="E181:F181"/>
-    <mergeCell ref="E182:F182"/>
-    <mergeCell ref="A168:A170"/>
-    <mergeCell ref="B168:B170"/>
-    <mergeCell ref="E168:F168"/>
-    <mergeCell ref="E169:F169"/>
-    <mergeCell ref="E170:F170"/>
-    <mergeCell ref="A174:A176"/>
-    <mergeCell ref="A32:B33"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="E32:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="B151:B159"/>
-    <mergeCell ref="C154:C156"/>
-    <mergeCell ref="D154:D156"/>
-    <mergeCell ref="C157:C159"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="A132:A134"/>
-    <mergeCell ref="B132:B134"/>
-    <mergeCell ref="A135:A137"/>
-    <mergeCell ref="B135:B137"/>
-    <mergeCell ref="B142:B150"/>
-    <mergeCell ref="C142:C144"/>
-    <mergeCell ref="D142:D144"/>
-    <mergeCell ref="A57:A70"/>
-    <mergeCell ref="B57:B70"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="D57:D60"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="A110:A121"/>
-    <mergeCell ref="B110:B121"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="B126:B128"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="E124:F125"/>
-    <mergeCell ref="A71:A85"/>
-    <mergeCell ref="A199:B199"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A55:B56"/>
-    <mergeCell ref="G158:G159"/>
-    <mergeCell ref="A191:B192"/>
-    <mergeCell ref="C191:D192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="E191:F191"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="E198:F198"/>
-    <mergeCell ref="G124:H124"/>
-    <mergeCell ref="H158:H159"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="G149:G150"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="H152:H153"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="A197:B197"/>
-    <mergeCell ref="E140:E141"/>
-    <mergeCell ref="F140:F141"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="G155:G156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="A151:A159"/>
+    <mergeCell ref="B71:B85"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="D76:D80"/>
+    <mergeCell ref="C81:C85"/>
+    <mergeCell ref="D81:D85"/>
+    <mergeCell ref="A98:A109"/>
+    <mergeCell ref="B98:B109"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="A86:A97"/>
+    <mergeCell ref="B86:B97"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.65625" header="0.39370078740157483" footer="0.39370078740157483"/>
